--- a/Output/Ahamove/04. OPS_METRICS/2026-07-lh-offload-kpi-workflow-explained.xlsx
+++ b/Output/Ahamove/04. OPS_METRICS/2026-07-lh-offload-kpi-workflow-explained.xlsx
@@ -7,11 +7,12 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Tổng Quan" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. FM Offload COT" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. SOC Offload COT" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. KPI Month &amp; Status" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Glossary" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="0. Source Mapping" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1. Tổng Quan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2. FM Offload COT" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3. SOC Offload COT" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4. KPI Month &amp; Status" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5. Glossary" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="17">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -111,6 +112,19 @@
       <color rgb="00000000"/>
       <sz val="8"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <i val="1"/>
+      <color rgb="00FF7F32"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="12">
     <fill>
@@ -180,7 +194,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -246,11 +260,69 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00E5E7EB"/>
+      </left>
+      <right style="thin">
+        <color rgb="00E5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E5E7EB"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E5E7EB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E5E7EB"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E5E7EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00E5E7EB"/>
+      </right>
+      <top style="thin">
+        <color rgb="00E5E7EB"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E5E7EB"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -388,6 +460,33 @@
     <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -753,6 +852,279 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="B2:E14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="4" max="4"/>
+    <col width="48" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="2" ht="30" customHeight="1">
+      <c r="B2" s="67" t="inlineStr">
+        <is>
+          <t>BẢN ĐỒ ĐỐI SOÁT DỮ LIỆU NGUỒN (DATA SOURCE MAPPING)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="24" customHeight="1">
+      <c r="B4" s="68" t="inlineStr">
+        <is>
+          <t>Sheet trong File Explained</t>
+        </is>
+      </c>
+      <c r="C4" s="68" t="inlineStr">
+        <is>
+          <t>Mục / Section Nội dung</t>
+        </is>
+      </c>
+      <c r="D4" s="68" t="inlineStr">
+        <is>
+          <t>File Nguồn Tương ứng (Source File)</t>
+        </is>
+      </c>
+      <c r="E4" s="68" t="inlineStr">
+        <is>
+          <t>Sheet &amp; Dòng/Cột Nguồn (Source Location)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="B5" s="63" t="inlineStr">
+        <is>
+          <t>1. Tổng Quan</t>
+        </is>
+      </c>
+      <c r="C5" s="63" t="inlineStr">
+        <is>
+          <t>Tổng quan Luồng KPI &amp; Sơ đồ Workflow</t>
+        </is>
+      </c>
+      <c r="D5" s="64" t="inlineStr">
+        <is>
+          <t>Review workflow LH offload KPI.xlsx</t>
+        </is>
+      </c>
+      <c r="E5" s="64" t="inlineStr">
+        <is>
+          <t>Sheet Info &amp; Sheet Code review (Dòng 1-3)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="B6" s="65" t="inlineStr">
+        <is>
+          <t>2. FM Offload COT</t>
+        </is>
+      </c>
+      <c r="C6" s="65" t="inlineStr">
+        <is>
+          <t>Logic 7 Bước FM Offload &amp; Công thức SLA End</t>
+        </is>
+      </c>
+      <c r="D6" s="66" t="inlineStr">
+        <is>
+          <t>LH logic review (1) (1).xlsx</t>
+        </is>
+      </c>
+      <c r="E6" s="66" t="inlineStr">
+        <is>
+          <t>Sheet FM_offload (Dòng 1 – 81)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="B7" s="63" t="inlineStr">
+        <is>
+          <t>3. SOC Offload COT</t>
+        </is>
+      </c>
+      <c r="C7" s="63" t="inlineStr">
+        <is>
+          <t>Mục 1 – 6: Nguồn Data, Cleanse &amp; 3TH Mapping COT</t>
+        </is>
+      </c>
+      <c r="D7" s="64" t="inlineStr">
+        <is>
+          <t>LH logic review (1) (1).xlsx</t>
+        </is>
+      </c>
+      <c r="E7" s="64" t="inlineStr">
+        <is>
+          <t>Sheet SOC_offload (Dòng 1 – 77, Cột A-M)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="B8" s="65" t="inlineStr">
+        <is>
+          <t>3. SOC Offload COT</t>
+        </is>
+      </c>
+      <c r="C8" s="65" t="inlineStr">
+        <is>
+          <t>Mục 7: Phân Lỗi offload_fault (SOC vs Linehaul Fault)</t>
+        </is>
+      </c>
+      <c r="D8" s="66" t="inlineStr">
+        <is>
+          <t>LH logic review (1) (1).xlsx</t>
+        </is>
+      </c>
+      <c r="E8" s="66" t="inlineStr">
+        <is>
+          <t>Sheet SOC_offload (Dòng 80 – 95, Cột N, O, P &amp; Cột A)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="22" customHeight="1">
+      <c r="B9" s="63" t="inlineStr">
+        <is>
+          <t>3. SOC Offload COT</t>
+        </is>
+      </c>
+      <c r="C9" s="63" t="inlineStr">
+        <is>
+          <t>Mục 8: Cơ chế &amp; Thuật toán FIFO (lh_adhoc_soc_miss_fifo)</t>
+        </is>
+      </c>
+      <c r="D9" s="64" t="inlineStr">
+        <is>
+          <t>LH logic review (1) (1).xlsx</t>
+        </is>
+      </c>
+      <c r="E9" s="64" t="inlineStr">
+        <is>
+          <t>Sheet SOC_offload (Dòng 130 – 178, Cột A-P)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="B10" s="65" t="inlineStr">
+        <is>
+          <t>3. SOC Offload COT</t>
+        </is>
+      </c>
+      <c r="C10" s="65" t="inlineStr">
+        <is>
+          <t>Mục 9: Logic KPI Month &amp; Bộ lọc WHERE</t>
+        </is>
+      </c>
+      <c r="D10" s="66" t="inlineStr">
+        <is>
+          <t>LH logic review (1) (1).xlsx</t>
+        </is>
+      </c>
+      <c r="E10" s="66" t="inlineStr">
+        <is>
+          <t>Sheet SOC_offload (Dòng 181 – 190, Cột A-E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="B11" s="63" t="inlineStr">
+        <is>
+          <t>3. SOC Offload COT</t>
+        </is>
+      </c>
+      <c r="C11" s="63" t="inlineStr">
+        <is>
+          <t>Mục 10: 4 Quy tắc Loại trừ Cuối khỏi KPI</t>
+        </is>
+      </c>
+      <c r="D11" s="64" t="inlineStr">
+        <is>
+          <t>LH logic review (1) (1).xlsx</t>
+        </is>
+      </c>
+      <c r="E11" s="64" t="inlineStr">
+        <is>
+          <t>Sheet SOC_offload (Dòng 191 – 203, Cột A-E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="B12" s="65" t="inlineStr">
+        <is>
+          <t>3. SOC Offload COT</t>
+        </is>
+      </c>
+      <c r="C12" s="65" t="inlineStr">
+        <is>
+          <t>Mục 11: Bảng Mapping Lý do Vận hành (explain_reason)</t>
+        </is>
+      </c>
+      <c r="D12" s="66" t="inlineStr">
+        <is>
+          <t>LH logic review (1) (1).xlsx</t>
+        </is>
+      </c>
+      <c r="E12" s="66" t="inlineStr">
+        <is>
+          <t>Sheet SOC_offload (Dòng 204 – 213, Cột A-E)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="B13" s="63" t="inlineStr">
+        <is>
+          <t>4. KPI Month &amp; Status</t>
+        </is>
+      </c>
+      <c r="C13" s="63" t="inlineStr">
+        <is>
+          <t>Bảng Status Code FMS &amp; Normalize Tên Station</t>
+        </is>
+      </c>
+      <c r="D13" s="64" t="inlineStr">
+        <is>
+          <t>Review workflow LH offload KPI.xlsx</t>
+        </is>
+      </c>
+      <c r="E13" s="64" t="inlineStr">
+        <is>
+          <t>Sheet Code review &amp; Sheet Liên quan đến phân loại station</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="B14" s="65" t="inlineStr">
+        <is>
+          <t>5. Glossary</t>
+        </is>
+      </c>
+      <c r="C14" s="65" t="inlineStr">
+        <is>
+          <t>Định nghĩa chuẩn hóa thuật ngữ Vận hành</t>
+        </is>
+      </c>
+      <c r="D14" s="66" t="inlineStr">
+        <is>
+          <t>Tổng hợp từ cả 2 File Source</t>
+        </is>
+      </c>
+      <c r="E14" s="66" t="inlineStr">
+        <is>
+          <t>Tất cả các Sheet trong 2 file nguồn</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:E2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -804,9 +1176,9 @@
           <t>MỤC ĐÍCH FILE</t>
         </is>
       </c>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="E6" s="7" t="n"/>
+      <c r="C6" s="9" t="n"/>
+      <c r="D6" s="9" t="n"/>
+      <c r="E6" s="10" t="n"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="B7" s="8" t="inlineStr">
@@ -826,9 +1198,9 @@
           <t>CẤU TRÚC FILE GỐC (4 SHEETS)</t>
         </is>
       </c>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="7" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="9" t="n"/>
+      <c r="E9" s="10" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
       <c r="B10" s="11" t="inlineStr">
@@ -921,9 +1293,9 @@
           <t>LUỒNG XỬ LÝ TỔNG THỂ</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="E16" s="7" t="n"/>
+      <c r="C16" s="9" t="n"/>
+      <c r="D16" s="9" t="n"/>
+      <c r="E16" s="10" t="n"/>
     </row>
     <row r="17" ht="34" customHeight="1">
       <c r="B17" s="14" t="inlineStr">
@@ -941,7 +1313,7 @@
           <t>Lấy dữ liệu từ bảng FM (dwd_spx_fleet_order_tracking_ri_vn) → mapping COT theo inbound_hub/station → xác định sla_end</t>
         </is>
       </c>
-      <c r="E17" s="17" t="n"/>
+      <c r="E17" s="10" t="n"/>
     </row>
     <row r="18" ht="34" customHeight="1">
       <c r="B18" s="18" t="inlineStr">
@@ -959,7 +1331,7 @@
           <t>Lấy dữ liệu từ bảng SOC BI (dwd_soc_kpi_ontime_history_v2) → xử lý COT window theo ngày/thứ/holiday → mapping 3 TH địa lý</t>
         </is>
       </c>
-      <c r="E18" s="21" t="n"/>
+      <c r="E18" s="10" t="n"/>
     </row>
     <row r="19" ht="34" customHeight="1">
       <c r="B19" s="22" t="inlineStr">
@@ -977,7 +1349,7 @@
           <t>Kết hợp data từ FM + SOC → xác định KPI month → output sla_eta_offload, kpi_month cho từng đơn</t>
         </is>
       </c>
-      <c r="E19" s="25" t="n"/>
+      <c r="E19" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -995,7 +1367,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1013,7 +1385,11 @@
   <sheetData>
     <row r="1" ht="10" customHeight="1">
       <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="n"/>
+      <c r="B1" s="69" t="inlineStr">
+        <is>
+          <t>📌 File Nguồn: Data sources/LH logic review (1) (1).xlsx [Sheet: FM_offload, Dòng 1-81]</t>
+        </is>
+      </c>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
@@ -1033,8 +1409,8 @@
           <t>1. NGUỒN DỮ LIỆU</t>
         </is>
       </c>
-      <c r="C4" s="28" t="n"/>
-      <c r="D4" s="29" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="10" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="B5" s="30" t="inlineStr">
@@ -1110,8 +1486,8 @@
           <t>2. MAPPING COT (Cut-off Time)</t>
         </is>
       </c>
-      <c r="C10" s="28" t="n"/>
-      <c r="D10" s="29" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="10" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="B11" s="30" t="inlineStr">
@@ -1190,8 +1566,8 @@
           <t>3. CỬA SỔ THỜI GIAN COT HỢP LỆ</t>
         </is>
       </c>
-      <c r="C17" s="28" t="n"/>
-      <c r="D17" s="29" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="10" t="n"/>
     </row>
     <row r="18" ht="46" customHeight="1">
       <c r="B18" s="31" t="inlineStr">
@@ -1202,8 +1578,8 @@
 → Nếu thỏa → đơn thuộc cửa sổ COT này → lấy COT tương ứng để tính SLA</t>
         </is>
       </c>
-      <c r="C18" s="32" t="n"/>
-      <c r="D18" s="33" t="n"/>
+      <c r="C18" s="9" t="n"/>
+      <c r="D18" s="10" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
       <c r="B20" s="27" t="inlineStr">
@@ -1211,8 +1587,8 @@
           <t>4. CÁC MỐC THỜI GIAN THEO STATUS</t>
         </is>
       </c>
-      <c r="C20" s="28" t="n"/>
-      <c r="D20" s="29" t="n"/>
+      <c r="C20" s="9" t="n"/>
+      <c r="D20" s="10" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
       <c r="B21" s="30" t="inlineStr">
@@ -1288,8 +1664,8 @@
           <t>5. LOGIC LẤY THỜI GIAN (ctime nhỏ nhất)</t>
         </is>
       </c>
-      <c r="C26" s="28" t="n"/>
-      <c r="D26" s="29" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="10" t="n"/>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="B27" s="37" t="inlineStr">
@@ -1300,8 +1676,8 @@
   soc_lhpacked = MIN(ctime) WHERE status IN (35, 412, 46)</t>
         </is>
       </c>
-      <c r="C27" s="38" t="n"/>
-      <c r="D27" s="39" t="n"/>
+      <c r="C27" s="9" t="n"/>
+      <c r="D27" s="10" t="n"/>
     </row>
     <row r="29" ht="22" customHeight="1">
       <c r="B29" s="27" t="inlineStr">
@@ -1309,8 +1685,8 @@
           <t>6. MỐC COT XÉT (ƯU TIÊN)</t>
         </is>
       </c>
-      <c r="C29" s="28" t="n"/>
-      <c r="D29" s="29" t="n"/>
+      <c r="C29" s="9" t="n"/>
+      <c r="D29" s="10" t="n"/>
     </row>
     <row r="30" ht="20" customHeight="1">
       <c r="B30" s="30" t="inlineStr">
@@ -1386,8 +1762,8 @@
           <t>7. XÁC ĐỊNH KPI MONTH</t>
         </is>
       </c>
-      <c r="C34" s="28" t="n"/>
-      <c r="D34" s="29" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="10" t="n"/>
     </row>
     <row r="35" ht="24" customHeight="1">
       <c r="B35" s="20" t="inlineStr">
@@ -1396,8 +1772,8 @@
   sla_end = actual_start_offload + eta_offload (từ sheet FM Offload COT)</t>
         </is>
       </c>
-      <c r="C35" s="40" t="n"/>
-      <c r="D35" s="21" t="n"/>
+      <c r="C35" s="9" t="n"/>
+      <c r="D35" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -1417,13 +1793,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -1435,7 +1811,11 @@
   <sheetData>
     <row r="1" ht="10" customHeight="1">
       <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="n"/>
+      <c r="B1" s="69" t="inlineStr">
+        <is>
+          <t>📌 File Nguồn: Data sources/LH logic review (1) (1).xlsx [Sheet: SOC_offload, Dòng 1-213, Cột A-P]</t>
+        </is>
+      </c>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
@@ -1455,8 +1835,8 @@
           <t>1. NGUỒN DỮ LIỆU</t>
         </is>
       </c>
-      <c r="C4" s="28" t="n"/>
-      <c r="D4" s="29" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="10" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="B5" s="30" t="inlineStr">
@@ -1532,8 +1912,8 @@
           <t>2. XỬ LÝ COT WINDOW (soc_cot_time_offload_cleanse)</t>
         </is>
       </c>
-      <c r="C10" s="28" t="n"/>
-      <c r="D10" s="29" t="n"/>
+      <c r="C10" s="9" t="n"/>
+      <c r="D10" s="10" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
       <c r="B11" s="30" t="inlineStr">
@@ -1629,8 +2009,8 @@
           <t>3. XÁC ĐỊNH actual_start_kpi_offload</t>
         </is>
       </c>
-      <c r="C17" s="28" t="n"/>
-      <c r="D17" s="29" t="n"/>
+      <c r="C17" s="9" t="n"/>
+      <c r="D17" s="10" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
       <c r="B18" s="30" t="inlineStr">
@@ -1706,8 +2086,8 @@
           <t>4. XỬ LÝ ĐỊA CHỈ BUYER (CŨ vs MỚI)</t>
         </is>
       </c>
-      <c r="C22" s="28" t="n"/>
-      <c r="D22" s="29" t="n"/>
+      <c r="C22" s="9" t="n"/>
+      <c r="D22" s="10" t="n"/>
     </row>
     <row r="23" ht="50" customHeight="1">
       <c r="B23" s="31" t="inlineStr">
@@ -1720,8 +2100,8 @@
   4. Logic ưu tiên: COALESCE(hub_zone.old_st, fact.buyr_st) — nếu không có địa chỉ cũ thì dùng địa chỉ mới</t>
         </is>
       </c>
-      <c r="C23" s="32" t="n"/>
-      <c r="D23" s="33" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="10" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="B25" s="27" t="inlineStr">
@@ -1729,8 +2109,8 @@
           <t>5. MAPPING COT — 3 TRƯỜNG HỢP ĐỊA LÝ</t>
         </is>
       </c>
-      <c r="C25" s="28" t="n"/>
-      <c r="D25" s="29" t="n"/>
+      <c r="C25" s="9" t="n"/>
+      <c r="D25" s="10" t="n"/>
     </row>
     <row r="26" ht="24" customHeight="1">
       <c r="B26" s="41" t="inlineStr">
@@ -1738,8 +2118,8 @@
           <t>TH1: CAS THEO TỈNH (buyer_city = ALL)</t>
         </is>
       </c>
-      <c r="C26" s="42" t="n"/>
-      <c r="D26" s="43" t="n"/>
+      <c r="C26" s="9" t="n"/>
+      <c r="D26" s="10" t="n"/>
     </row>
     <row r="27" ht="36" customHeight="1">
       <c r="B27" s="44" t="inlineStr">
@@ -1753,7 +2133,7 @@
 AND offload.buyer_city IN ('ALL')</t>
         </is>
       </c>
-      <c r="D27" s="45" t="n"/>
+      <c r="D27" s="10" t="n"/>
     </row>
     <row r="28" ht="24" customHeight="1">
       <c r="B28" s="44" t="inlineStr">
@@ -1766,7 +2146,7 @@
           <t>offload.buyer_state = COALESCE(hub_zone.old_st, fact.buyr_st)</t>
         </is>
       </c>
-      <c r="D28" s="45" t="n"/>
+      <c r="D28" s="10" t="n"/>
     </row>
     <row r="29" ht="36" customHeight="1">
       <c r="B29" s="44" t="inlineStr">
@@ -1780,7 +2160,7 @@
 buycer_city được chuẩn hóa: nếu không có trong COT table thì = 'ALL'</t>
         </is>
       </c>
-      <c r="D29" s="45" t="n"/>
+      <c r="D29" s="10" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1">
       <c r="B30" s="44" t="inlineStr">
@@ -1793,7 +2173,7 @@
           <t>Đơn giao tỉnh nhỏ, COT theo tỉnh</t>
         </is>
       </c>
-      <c r="D30" s="45" t="n"/>
+      <c r="D30" s="10" t="n"/>
     </row>
     <row r="31" ht="6" customHeight="1"/>
     <row r="34" ht="24" customHeight="1">
@@ -1802,8 +2182,8 @@
           <t>TH2: CAS THEO QUẬN/HUYỆN (buyer_city cụ thể)</t>
         </is>
       </c>
-      <c r="C34" s="47" t="n"/>
-      <c r="D34" s="48" t="n"/>
+      <c r="C34" s="9" t="n"/>
+      <c r="D34" s="10" t="n"/>
     </row>
     <row r="35" ht="36" customHeight="1">
       <c r="B35" s="49" t="inlineStr">
@@ -1817,7 +2197,7 @@
 AND offload_city.buyer_city NOT IN ('ALL')</t>
         </is>
       </c>
-      <c r="D35" s="45" t="n"/>
+      <c r="D35" s="10" t="n"/>
     </row>
     <row r="36" ht="36" customHeight="1">
       <c r="B36" s="49" t="inlineStr">
@@ -1831,7 +2211,7 @@
 AND offload_city.buyer_city = COALESCE(hub_zone.old_ct, fact.buyr_ct)</t>
         </is>
       </c>
-      <c r="D36" s="45" t="n"/>
+      <c r="D36" s="10" t="n"/>
     </row>
     <row r="37" ht="36" customHeight="1">
       <c r="B37" s="49" t="inlineStr">
@@ -1845,7 +2225,7 @@
 COALESCE đảm bảo dùng địa chỉ cũ để tránh sai lệch hệ thống địa chỉ mới</t>
         </is>
       </c>
-      <c r="D37" s="45" t="n"/>
+      <c r="D37" s="10" t="n"/>
     </row>
     <row r="38" ht="24" customHeight="1">
       <c r="B38" s="49" t="inlineStr">
@@ -1858,7 +2238,7 @@
           <t>Đơn HCM/HN — COT riêng theo quận</t>
         </is>
       </c>
-      <c r="D38" s="45" t="n"/>
+      <c r="D38" s="10" t="n"/>
     </row>
     <row r="39" ht="6" customHeight="1"/>
     <row r="42" ht="24" customHeight="1">
@@ -1867,8 +2247,8 @@
           <t>TH3: CAS THEO NEXT STATION (biết route cụ thể)</t>
         </is>
       </c>
-      <c r="C42" s="51" t="n"/>
-      <c r="D42" s="25" t="n"/>
+      <c r="C42" s="9" t="n"/>
+      <c r="D42" s="10" t="n"/>
     </row>
     <row r="43" ht="24" customHeight="1">
       <c r="B43" s="52" t="inlineStr">
@@ -1881,7 +2261,7 @@
           <t>next_station_name IS NOT NULL</t>
         </is>
       </c>
-      <c r="D43" s="45" t="n"/>
+      <c r="D43" s="10" t="n"/>
     </row>
     <row r="44" ht="24" customHeight="1">
       <c r="B44" s="52" t="inlineStr">
@@ -1894,7 +2274,7 @@
           <t>offload_next_station.next_station_name = fact.next_station_name</t>
         </is>
       </c>
-      <c r="D44" s="45" t="n"/>
+      <c r="D44" s="10" t="n"/>
     </row>
     <row r="45" ht="36" customHeight="1">
       <c r="B45" s="52" t="inlineStr">
@@ -1908,7 +2288,7 @@
 COT theo lịch chạy giữa 2 hub cụ thể — chính xác nhất</t>
         </is>
       </c>
-      <c r="D45" s="45" t="n"/>
+      <c r="D45" s="10" t="n"/>
     </row>
     <row r="46" ht="24" customHeight="1">
       <c r="B46" s="52" t="inlineStr">
@@ -1921,7 +2301,7 @@
           <t>Đơn transit giữa 2 hub — COT route cụ thể</t>
         </is>
       </c>
-      <c r="D46" s="45" t="n"/>
+      <c r="D46" s="10" t="n"/>
     </row>
     <row r="47" ht="6" customHeight="1"/>
     <row r="50" ht="22" customHeight="1">
@@ -1930,8 +2310,8 @@
           <t>6. TỔNG HỢP COT TỪ 3 TRƯỜNG HỢP (Ưu tiên COT chặt nhất)</t>
         </is>
       </c>
-      <c r="C50" s="28" t="n"/>
-      <c r="D50" s="29" t="n"/>
+      <c r="C50" s="9" t="n"/>
+      <c r="D50" s="10" t="n"/>
     </row>
     <row r="51" ht="20" customHeight="1">
       <c r="B51" s="30" t="inlineStr">
@@ -2011,11 +2391,766 @@
 MIN() để loại bỏ trùng lặp nếu nhiều row match, chọn cửa sổ COT chặt nhất (sớm nhất).</t>
         </is>
       </c>
-      <c r="C55" s="40" t="n"/>
-      <c r="D55" s="21" t="n"/>
+      <c r="C55" s="9" t="n"/>
+      <c r="D55" s="10" t="n"/>
+    </row>
+    <row r="58" ht="24" customHeight="1">
+      <c r="B58" s="61" t="inlineStr">
+        <is>
+          <t>7. PHÂN LỖI KPI OFFLOAD (offload_fault: Lỗi thuộc về ai?) — Source Cột N, O, P (Dòng 80-95)</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="20" customHeight="1">
+      <c r="B59" s="62" t="inlineStr">
+        <is>
+          <t>Điều kiện (Conditions)</t>
+        </is>
+      </c>
+      <c r="C59" s="62" t="inlineStr">
+        <is>
+          <t>Gán lỗi (Fault)</t>
+        </is>
+      </c>
+      <c r="D59" s="62" t="inlineStr">
+        <is>
+          <t>Ý nghĩa &amp; Mô tả chi tiết Vận hành</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="22" customHeight="1">
+      <c r="B60" s="63" t="inlineStr">
+        <is>
+          <t>LH đến trễ (ticket)</t>
+        </is>
+      </c>
+      <c r="C60" s="64" t="inlineStr">
+        <is>
+          <t>SOC Transfer Late To TS</t>
+        </is>
+      </c>
+      <c r="D60" s="64" t="inlineStr">
+        <is>
+          <t>SOC bàn giao trễ cho Linehaul Transit</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="22" customHeight="1">
+      <c r="B61" s="65" t="inlineStr">
+        <is>
+          <t>CS ticket / Adhoc GSheet / SIP</t>
+        </is>
+      </c>
+      <c r="C61" s="66" t="inlineStr">
+        <is>
+          <t>No Fault</t>
+        </is>
+      </c>
+      <c r="D61" s="66" t="inlineStr">
+        <is>
+          <t>Lỗi khách quan, được phép loại trừ (Ticket CS/Adhoc/SIP)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="22" customHeight="1">
+      <c r="B62" s="63" t="inlineStr">
+        <is>
+          <t>Missing COT</t>
+        </is>
+      </c>
+      <c r="C62" s="64" t="inlineStr">
+        <is>
+          <t>No Fault</t>
+        </is>
+      </c>
+      <c r="D62" s="64" t="inlineStr">
+        <is>
+          <t>Chưa có cấu hình mốc COT chuẩn trên hệ thống Master Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="22" customHeight="1">
+      <c r="B63" s="65" t="inlineStr">
+        <is>
+          <t>Missing LH scan + có COT</t>
+        </is>
+      </c>
+      <c r="C63" s="66" t="inlineStr">
+        <is>
+          <t>SOC Fault</t>
+        </is>
+      </c>
+      <c r="D63" s="66" t="inlineStr">
+        <is>
+          <t>SOC thiếu trạng thái scan Linehaul Packed dù đã có COT</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="22" customHeight="1">
+      <c r="B64" s="63" t="inlineStr">
+        <is>
+          <t>Có ticket cấp xe/overcap + actual_end &lt;= SLA ontime</t>
+        </is>
+      </c>
+      <c r="C64" s="64" t="inlineStr">
+        <is>
+          <t>No Fault</t>
+        </is>
+      </c>
+      <c r="D64" s="64" t="inlineStr">
+        <is>
+          <t>Ticket tăng năng lực xe được duyệt, SOC hoàn thành đúng SLA gia hạn</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="22" customHeight="1">
+      <c r="B65" s="65" t="inlineStr">
+        <is>
+          <t>actual_end &lt;= SLA ontime origin</t>
+        </is>
+      </c>
+      <c r="C65" s="66" t="inlineStr">
+        <is>
+          <t>No Fault</t>
+        </is>
+      </c>
+      <c r="D65" s="66" t="inlineStr">
+        <is>
+          <t>SOC hoàn thành đúng khung SLA gốc</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="22" customHeight="1">
+      <c r="B66" s="63" t="inlineStr">
+        <is>
+          <t>actual_end &gt; SLA ontime origin + LH đến trễ &gt; 2h</t>
+        </is>
+      </c>
+      <c r="C66" s="64" t="inlineStr">
+        <is>
+          <t>SOC - Linehaul Fault</t>
+        </is>
+      </c>
+      <c r="D66" s="64" t="inlineStr">
+        <is>
+          <t>SOC CHOOSE THE NEXT LINEHAUL TRIP -&gt; Có thể Linehaul tới trễ &gt; 2h</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="22" customHeight="1">
+      <c r="B67" s="65" t="inlineStr">
+        <is>
+          <t>ckin_gof_outbound (within 500m) = 'NO' + actual_end &lt;= SLA_ontime</t>
+        </is>
+      </c>
+      <c r="C67" s="66" t="inlineStr">
+        <is>
+          <t>No Fault</t>
+        </is>
+      </c>
+      <c r="D67" s="66" t="inlineStr">
+        <is>
+          <t>LH không checkin vào cổng nhưng SOC vẫn xử lý kịp SLA</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="22" customHeight="1">
+      <c r="B68" s="63" t="inlineStr">
+        <is>
+          <t>ckin_gof_outbound (within 500m) = 'NO' + actual_end &gt; SLA_ontime</t>
+        </is>
+      </c>
+      <c r="C68" s="64" t="inlineStr">
+        <is>
+          <t>Linehaul Fault</t>
+        </is>
+      </c>
+      <c r="D68" s="64" t="inlineStr">
+        <is>
+          <t>LH không vào cổng -&gt; SOC bị trễ dây chuyền</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="22" customHeight="1">
+      <c r="B69" s="65" t="inlineStr">
+        <is>
+          <t>ckin_gof_outbound (within 500m) = 'YES' + trước 15/9/2024</t>
+        </is>
+      </c>
+      <c r="C69" s="66" t="inlineStr">
+        <is>
+          <t>Linehaul Fault</t>
+        </is>
+      </c>
+      <c r="D69" s="66" t="inlineStr">
+        <is>
+          <t>Rule cũ trước 15/9/2024, chưa phân tầng thời gian xe đến</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="22" customHeight="1">
+      <c r="B70" s="63" t="inlineStr">
+        <is>
+          <t>ckin_gof_outbound (within 500m) = 'YES' + từ 15/9/2024 + LH đến sớm &gt;=30'</t>
+        </is>
+      </c>
+      <c r="C70" s="64" t="inlineStr">
+        <is>
+          <t>Exclude LH Fault</t>
+        </is>
+      </c>
+      <c r="D70" s="64" t="inlineStr">
+        <is>
+          <t>LH đến sớm đủ (&gt;=30p), trễ là do SOC tự xử lý chậm</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="22" customHeight="1">
+      <c r="B71" s="65" t="inlineStr">
+        <is>
+          <t>ckin_gof_outbound (within 500m) = 'YES' + từ 15/9/2024 + LH đến sát SLA SOC (+-30')</t>
+        </is>
+      </c>
+      <c r="C71" s="66" t="inlineStr">
+        <is>
+          <t>Linehaul Fault Late Near COT SOC</t>
+        </is>
+      </c>
+      <c r="D71" s="66" t="inlineStr">
+        <is>
+          <t>LH đến quá sát giờ COT SOC (trễ vừa phải)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="22" customHeight="1">
+      <c r="B72" s="63" t="inlineStr">
+        <is>
+          <t>ckin_gof_outbound (within 500m) = 'YES' + từ 15/9/2024 + LH đến sau SLA SOC</t>
+        </is>
+      </c>
+      <c r="C72" s="70" t="n"/>
+      <c r="D72" s="71" t="n"/>
+    </row>
+    <row r="73" ht="20" customHeight="1"/>
+    <row r="74" ht="24" customHeight="1">
+      <c r="B74" s="61" t="inlineStr">
+        <is>
+          <t>8. CƠ CHẾ KIỂM SOÁT FIFO (lh_adhoc_soc_miss_fifo) — Dòng 130-178 Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="20" customHeight="1">
+      <c r="B75" s="62" t="inlineStr">
+        <is>
+          <t>Khái niệm &amp; Thuật toán</t>
+        </is>
+      </c>
+      <c r="C75" s="62" t="inlineStr">
+        <is>
+          <t>Chi tiết Quy tắc SQL &amp; Công thức</t>
+        </is>
+      </c>
+      <c r="D75" s="62" t="inlineStr">
+        <is>
+          <t>Tác động KPI &amp; Xử lý</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="22" customHeight="1">
+      <c r="B76" s="63" t="inlineStr">
+        <is>
+          <t>1. Nguyên tắc FIFO</t>
+        </is>
+      </c>
+      <c r="C76" s="64" t="inlineStr">
+        <is>
+          <t>First In, First Out: Đơn đến SOC trước phải packed &amp; bàn giao trước</t>
+        </is>
+      </c>
+      <c r="D76" s="64" t="inlineStr">
+        <is>
+          <t>Đảm bảo công bằng trong luồng xử lý hàng hóa SOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="22" customHeight="1">
+      <c r="B77" s="65" t="inlineStr">
+        <is>
+          <t>2. Dấu hiệu Miss FIFO</t>
+        </is>
+      </c>
+      <c r="C77" s="66" t="inlineStr">
+        <is>
+          <t>SOC pack đơn deadline muộn trước, để đơn deadline sớm bị trễ</t>
+        </is>
+      </c>
+      <c r="D77" s="66" t="inlineStr">
+        <is>
+          <t>Gây ra trễ dây chuyền cho các đơn đến trước</t>
+        </is>
+      </c>
+    </row>
+    <row r="78" ht="22" customHeight="1">
+      <c r="B78" s="63" t="inlineStr">
+        <is>
+          <t>3. Cờ nhận diện 1</t>
+        </is>
+      </c>
+      <c r="C78" s="64" t="inlineStr">
+        <is>
+          <t>don_thuoc_cot_sau = 'yes' (sla_eta_offload &lt; sla_lhpacked_eta_ontime)</t>
+        </is>
+      </c>
+      <c r="D78" s="64" t="inlineStr">
+        <is>
+          <t>Đơn có deadline LH sớm hơn deadline SOC (SOC có thể pack sau)</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="22" customHeight="1">
+      <c r="B79" s="65" t="inlineStr">
+        <is>
+          <t>4. Cờ nhận diện 2</t>
+        </is>
+      </c>
+      <c r="C79" s="66" t="inlineStr">
+        <is>
+          <t>don_late_trong_cot = 'yes' (kpi_lhpacked_ontime = 'Late')</t>
+        </is>
+      </c>
+      <c r="D79" s="66" t="inlineStr">
+        <is>
+          <t>Đơn thực tế bị trễ trong khung COT SOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="22" customHeight="1">
+      <c r="B80" s="63" t="inlineStr">
+        <is>
+          <t>5. Điều kiện nghi ngờ</t>
+        </is>
+      </c>
+      <c r="C80" s="64" t="inlineStr">
+        <is>
+          <t>GROUP BY (date, station, cot_lh, cot_soc) HAVING vol_don_thuoc_cot_sau &gt; 0 AND vol_don_late_trong_cot &gt; 0</t>
+        </is>
+      </c>
+      <c r="D80" s="64" t="inlineStr">
+        <is>
+          <t>Trong cùng slot vừa có đơn trễ vừa có đơn COT sau -&gt; vi phạm FIFO</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="22" customHeight="1">
+      <c r="B81" s="65" t="inlineStr">
+        <is>
+          <t>6. Phân bổ Miss FIFO (N1)</t>
+        </is>
+      </c>
+      <c r="C81" s="66" t="inlineStr">
+        <is>
+          <t>Nếu vol_don_thuoc_cot_sau &gt;= vol_don_late_trong_cot</t>
+        </is>
+      </c>
+      <c r="D81" s="66" t="inlineStr">
+        <is>
+          <t>Toàn bộ đơn trễ trong slot đều tính là miss_fifo</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="22" customHeight="1">
+      <c r="B82" s="63" t="inlineStr">
+        <is>
+          <t>7. Phân bổ Miss FIFO (N2)</t>
+        </is>
+      </c>
+      <c r="C82" s="64" t="inlineStr">
+        <is>
+          <t>Nếu vol_don_late_trong_cot &gt; vol_don_thuoc_cot_sau</t>
+        </is>
+      </c>
+      <c r="D82" s="64" t="inlineStr">
+        <is>
+          <t>Số đơn miss_fifo = GREATEST(late - cot_sau, cot_sau) xếp theo soc_received</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="22" customHeight="1">
+      <c r="B83" s="65" t="inlineStr">
+        <is>
+          <t>8. Quy chuẩn COT</t>
+        </is>
+      </c>
+      <c r="C83" s="66" t="inlineStr">
+        <is>
+          <t>sla_eta_offload - INTERVAL '6' MINUTE &amp; sla_lhpacked_eta_ontime - INTERVAL '6' MINUTE</t>
+        </is>
+      </c>
+      <c r="D83" s="66" t="inlineStr">
+        <is>
+          <t>Trừ 6 phút để quy chuẩn về mốc COT chung</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="22" customHeight="1">
+      <c r="B84" s="63" t="inlineStr">
+        <is>
+          <t>9. Loại khỏi KPI</t>
+        </is>
+      </c>
+      <c r="C84" s="70" t="n"/>
+      <c r="D84" s="71" t="n"/>
+    </row>
+    <row r="85" ht="20" customHeight="1"/>
+    <row r="86" ht="24" customHeight="1">
+      <c r="B86" s="61" t="inlineStr">
+        <is>
+          <t>9. LOGIC KPI MONTH &amp; BỘ LỌC ĐIỀU KIỆN (WHERE) — Dòng 181-190 Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="87" ht="20" customHeight="1">
+      <c r="B87" s="62" t="inlineStr">
+        <is>
+          <t>Mục</t>
+        </is>
+      </c>
+      <c r="C87" s="62" t="inlineStr">
+        <is>
+          <t>Logic SQL / Quy tắc</t>
+        </is>
+      </c>
+      <c r="D87" s="62" t="inlineStr">
+        <is>
+          <t>Ghi chú</t>
+        </is>
+      </c>
+    </row>
+    <row r="88" ht="22" customHeight="1">
+      <c r="B88" s="63" t="inlineStr">
+        <is>
+          <t>Chính sách trước 15/03/2026</t>
+        </is>
+      </c>
+      <c r="C88" s="64" t="inlineStr">
+        <is>
+          <t>IF DAY(sla_eta_offload) &lt; 15 THEN Month-1 ELSE Month hiện tại</t>
+        </is>
+      </c>
+      <c r="D88" s="64" t="inlineStr">
+        <is>
+          <t>Áp dụng theo chu kỳ chốt số cũ</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="22" customHeight="1">
+      <c r="B89" s="65" t="inlineStr">
+        <is>
+          <t>Giai đoạn 15/03 - 31/03/2026</t>
+        </is>
+      </c>
+      <c r="C89" s="66" t="inlineStr">
+        <is>
+          <t>Hardcode cố định date '2026-03-01'</t>
+        </is>
+      </c>
+      <c r="D89" s="66" t="inlineStr">
+        <is>
+          <t>Giai đoạn bản lề chuyển đổi chính sách</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="22" customHeight="1">
+      <c r="B90" s="63" t="inlineStr">
+        <is>
+          <t>Chính sách từ 01/04/2026</t>
+        </is>
+      </c>
+      <c r="C90" s="64" t="inlineStr">
+        <is>
+          <t>DATE_TRUNC('MONTH', date(sla_eta_offload))</t>
+        </is>
+      </c>
+      <c r="D90" s="64" t="inlineStr">
+        <is>
+          <t>Chuẩn hóa tính theo tháng thực tế của SLA ETA</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="22" customHeight="1">
+      <c r="B91" s="65" t="inlineStr">
+        <is>
+          <t>Filter kpi_offload</t>
+        </is>
+      </c>
+      <c r="C91" s="66" t="inlineStr">
+        <is>
+          <t>WHERE kpi_offload IN ('Not Offload', 'Offload')</t>
+        </is>
+      </c>
+      <c r="D91" s="66" t="inlineStr">
+        <is>
+          <t>Chỉ lấy các đơn đã hoàn tất phán định</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="22" customHeight="1">
+      <c r="B92" s="63" t="inlineStr">
+        <is>
+          <t>Filter offload_fault</t>
+        </is>
+      </c>
+      <c r="C92" s="64" t="inlineStr">
+        <is>
+          <t>AND offload_fault NOT IN ('SOC Fault - Missing stt', 'SOC Fault')</t>
+        </is>
+      </c>
+      <c r="D92" s="64" t="inlineStr">
+        <is>
+          <t>Loại các lỗi do SOC thiếu trạng thái scan</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="22" customHeight="1">
+      <c r="B93" s="65" t="inlineStr">
+        <is>
+          <t>Filter mốc thời gian</t>
+        </is>
+      </c>
+      <c r="C93" s="70" t="n"/>
+      <c r="D93" s="71" t="n"/>
+    </row>
+    <row r="94" ht="20" customHeight="1"/>
+    <row r="95" ht="24" customHeight="1">
+      <c r="B95" s="61" t="inlineStr">
+        <is>
+          <t>10. 4 QUY TẮC LOẠI TRỪ BỔ SUNG KHỎI KPI — Dòng 191-203 Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="96" ht="20" customHeight="1">
+      <c r="B96" s="62" t="inlineStr">
+        <is>
+          <t>Mã loại trừ</t>
+        </is>
+      </c>
+      <c r="C96" s="62" t="inlineStr">
+        <is>
+          <t>Chi tiết Nguồn dữ liệu &amp; Điều kiện</t>
+        </is>
+      </c>
+      <c r="D96" s="62" t="inlineStr">
+        <is>
+          <t>Phạm vi Tác động</t>
+        </is>
+      </c>
+    </row>
+    <row r="97" ht="22" customHeight="1">
+      <c r="B97" s="63" t="inlineStr">
+        <is>
+          <t>1. hub_hold_hang</t>
+        </is>
+      </c>
+      <c r="C97" s="64" t="inlineStr">
+        <is>
+          <t>Ticket status Resolved/Opex Reviewing (HUB yeu cau hold hang) + GSheet hold overdue/thuong (regex parse key)</t>
+        </is>
+      </c>
+      <c r="D97" s="64" t="inlineStr">
+        <is>
+          <t>Loại khỏi cả tử và mẫu KPI do Hub chủ động hold</t>
+        </is>
+      </c>
+    </row>
+    <row r="98" ht="22" customHeight="1">
+      <c r="B98" s="65" t="inlineStr">
+        <is>
+          <t>2. soc_miss_fifo</t>
+        </is>
+      </c>
+      <c r="C98" s="66" t="inlineStr">
+        <is>
+          <t>Đơn từ soc_kpi_ontime_outdate_v2 có soc_lhpacked &gt;= sla_lhpacked_eta_ontime_extend_1_cot (trễ &gt; 1 COT từ 2026-01-01)</t>
+        </is>
+      </c>
+      <c r="D98" s="66" t="inlineStr">
+        <is>
+          <t>Loại hoàn toàn đơn packed quá trễ khỏi mẫu</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="22" customHeight="1">
+      <c r="B99" s="63" t="inlineStr">
+        <is>
+          <t>3. remove_portal</t>
+        </is>
+      </c>
+      <c r="C99" s="64" t="inlineStr">
+        <is>
+          <t>Đơn có ticket KPI metric "% Tỷ lệ không rớt kết nối hàng" trạng thái Resolved từ 2026-01-01</t>
+        </is>
+      </c>
+      <c r="D99" s="64" t="inlineStr">
+        <is>
+          <t>Loại bỏ theo kết quả xử lý ticket khiếu nại</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="22" customHeight="1">
+      <c r="B100" s="65" t="inlineStr">
+        <is>
+          <t>4. gsheet_offload_remove</t>
+        </is>
+      </c>
+      <c r="C100" s="70" t="n"/>
+      <c r="D100" s="71" t="n"/>
+    </row>
+    <row r="101" ht="20" customHeight="1"/>
+    <row r="102" ht="24" customHeight="1">
+      <c r="B102" s="61" t="inlineStr">
+        <is>
+          <t>11. MAPPING LÝ DO GIẢI THÍCH (explain_reason) — Dòng 204-213 Source</t>
+        </is>
+      </c>
+    </row>
+    <row r="103" ht="20" customHeight="1">
+      <c r="B103" s="62" t="inlineStr">
+        <is>
+          <t>Giá trị offload_fault / Remark</t>
+        </is>
+      </c>
+      <c r="C103" s="62" t="inlineStr">
+        <is>
+          <t>Lý do hiển thị Vận hành (explain_reason)</t>
+        </is>
+      </c>
+      <c r="D103" s="62" t="inlineStr">
+        <is>
+          <t>Hướng xử lý Vận hành</t>
+        </is>
+      </c>
+    </row>
+    <row r="104" ht="22" customHeight="1">
+      <c r="B104" s="63" t="inlineStr">
+        <is>
+          <t>Transfer Late / SOC Transfer Late To TS</t>
+        </is>
+      </c>
+      <c r="C104" s="64" t="inlineStr">
+        <is>
+          <t>SOC chuyển đơn late cho LH</t>
+        </is>
+      </c>
+      <c r="D104" s="64" t="inlineStr">
+        <is>
+          <t>SOC cần tối ưu thời gian gom hàng &amp; bàn giao</t>
+        </is>
+      </c>
+    </row>
+    <row r="105" ht="22" customHeight="1">
+      <c r="B105" s="65" t="inlineStr">
+        <is>
+          <t>SOC - Linehaul Fault (SOC not ontime)</t>
+        </is>
+      </c>
+      <c r="C105" s="66" t="inlineStr">
+        <is>
+          <t>LH đến trễ COT &amp; SOC không ontime</t>
+        </is>
+      </c>
+      <c r="D105" s="66" t="inlineStr">
+        <is>
+          <t>Cả 2 bên cùng trễ, cần xem xét mốc bàn giao thực tế</t>
+        </is>
+      </c>
+    </row>
+    <row r="106" ht="22" customHeight="1">
+      <c r="B106" s="63" t="inlineStr">
+        <is>
+          <t>Trễ COT LH &amp; ckin_gof_outbound = 'NO'</t>
+        </is>
+      </c>
+      <c r="C106" s="64" t="inlineStr">
+        <is>
+          <t>Lỗi check in ngoài phạm vi</t>
+        </is>
+      </c>
+      <c r="D106" s="64" t="inlineStr">
+        <is>
+          <t>Tài xế Linehaul không check-in đúng tọa độ quy định</t>
+        </is>
+      </c>
+    </row>
+    <row r="107" ht="22" customHeight="1">
+      <c r="B107" s="65" t="inlineStr">
+        <is>
+          <t>Linehaul Fault Late COT SOC</t>
+        </is>
+      </c>
+      <c r="C107" s="66" t="inlineStr">
+        <is>
+          <t>LH trễ COT SOC</t>
+        </is>
+      </c>
+      <c r="D107" s="66" t="inlineStr">
+        <is>
+          <t>Lỗi hoàn toàn do xe Linehaul đến trễ so với COT SOC</t>
+        </is>
+      </c>
+    </row>
+    <row r="108" ht="22" customHeight="1">
+      <c r="B108" s="63" t="inlineStr">
+        <is>
+          <t>Linehaul Fault Late Near COT SOC</t>
+        </is>
+      </c>
+      <c r="C108" s="64" t="inlineStr">
+        <is>
+          <t>LH đến sát COT SOC</t>
+        </is>
+      </c>
+      <c r="D108" s="64" t="inlineStr">
+        <is>
+          <t>Linehaul đến quá sát giờ COT làm SOC không kịp xử lý</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="22" customHeight="1">
+      <c r="B109" s="65" t="inlineStr">
+        <is>
+          <t>Thiếu COT SOC</t>
+        </is>
+      </c>
+      <c r="C109" s="66" t="inlineStr">
+        <is>
+          <t>Thiếu COT SOC</t>
+        </is>
+      </c>
+      <c r="D109" s="66" t="inlineStr">
+        <is>
+          <t>Bổ sung cấu hình COT SOC trên hệ thống Master Data</t>
+        </is>
+      </c>
+    </row>
+    <row r="110" ht="22" customHeight="1">
+      <c r="B110" s="63" t="inlineStr">
+        <is>
+          <t>Khác (ELSE)</t>
+        </is>
+      </c>
+      <c r="C110" s="64" t="inlineStr">
+        <is>
+          <t>Checking</t>
+        </is>
+      </c>
+      <c r="D110" s="64" t="inlineStr">
+        <is>
+          <t>Bộ phận OPS/BI tiếp tục kiểm tra dữ liệu chi tiết</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="33">
     <mergeCell ref="B42:D42"/>
     <mergeCell ref="C30:D30"/>
     <mergeCell ref="B23:D23"/>
@@ -2025,8 +3160,11 @@
     <mergeCell ref="B34:D34"/>
     <mergeCell ref="B10:D10"/>
     <mergeCell ref="C29:D29"/>
+    <mergeCell ref="B84:D84"/>
+    <mergeCell ref="B74:D74"/>
     <mergeCell ref="C44:D44"/>
     <mergeCell ref="B55:D55"/>
+    <mergeCell ref="B95:D95"/>
     <mergeCell ref="C43:D43"/>
     <mergeCell ref="C46:D46"/>
     <mergeCell ref="C27:D27"/>
@@ -2034,10 +3172,16 @@
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="B26:D26"/>
     <mergeCell ref="C36:D36"/>
+    <mergeCell ref="B100:D100"/>
     <mergeCell ref="B25:D25"/>
+    <mergeCell ref="B86:D86"/>
+    <mergeCell ref="B72:D72"/>
     <mergeCell ref="C38:D38"/>
+    <mergeCell ref="B102:D102"/>
     <mergeCell ref="B22:D22"/>
+    <mergeCell ref="B93:D93"/>
     <mergeCell ref="C37:D37"/>
+    <mergeCell ref="B58:D58"/>
     <mergeCell ref="C28:D28"/>
     <mergeCell ref="B2:D2"/>
   </mergeCells>
@@ -2045,7 +3189,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2063,7 +3207,11 @@
   <sheetData>
     <row r="1" ht="10" customHeight="1">
       <c r="A1" s="1" t="n"/>
-      <c r="B1" s="1" t="n"/>
+      <c r="B1" s="69" t="inlineStr">
+        <is>
+          <t>📌 File Nguồn: Data sources/Review workflow LH offload KPI.xlsx [Sheet: Code review &amp; Station Classification]</t>
+        </is>
+      </c>
       <c r="C1" s="1" t="n"/>
       <c r="D1" s="1" t="n"/>
       <c r="E1" s="1" t="n"/>
@@ -2083,8 +3231,8 @@
           <t>1. LOGIC XÁC ĐỊNH KPI MONTH (SOC — theo sla_eta_offload)</t>
         </is>
       </c>
-      <c r="C4" s="28" t="n"/>
-      <c r="D4" s="29" t="n"/>
+      <c r="C4" s="9" t="n"/>
+      <c r="D4" s="10" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
       <c r="B5" s="30" t="inlineStr">
@@ -2164,8 +3312,8 @@
 → Hai nguồn có logic xác định KPI month khác nhau — cần chú ý khi merge</t>
         </is>
       </c>
-      <c r="C9" s="40" t="n"/>
-      <c r="D9" s="21" t="n"/>
+      <c r="C9" s="9" t="n"/>
+      <c r="D9" s="10" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="27" t="inlineStr">
@@ -2173,8 +3321,8 @@
           <t>2. BẢNG MAPPING STATUS CODE → TÊN CỘT SQL</t>
         </is>
       </c>
-      <c r="C11" s="28" t="n"/>
-      <c r="D11" s="29" t="n"/>
+      <c r="C11" s="9" t="n"/>
+      <c r="D11" s="10" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
       <c r="B12" s="30" t="inlineStr">
@@ -2352,8 +3500,8 @@
           <t>3. SQL SNIPPET — LẤY THỜI GIAN THEO STATUS (update 2025-03-18)</t>
         </is>
       </c>
-      <c r="C23" s="28" t="n"/>
-      <c r="D23" s="29" t="n"/>
+      <c r="C23" s="9" t="n"/>
+      <c r="D23" s="10" t="n"/>
     </row>
     <row r="24" ht="28" customHeight="1">
       <c r="B24" s="56" t="inlineStr">
@@ -2366,7 +3514,7 @@
           <t>,MIN(CASE WHEN status IN (8, 400, 42) THEN FROM_UNIXTIME(ctime - 3600) ELSE NULL END) AS fm_inbound</t>
         </is>
       </c>
-      <c r="D24" s="39" t="n"/>
+      <c r="D24" s="10" t="n"/>
     </row>
     <row r="25" ht="28" customHeight="1">
       <c r="B25" s="56" t="inlineStr">
@@ -2379,7 +3527,7 @@
           <t>,MIN_BY(CASE WHEN status IN (8, 400, 42) THEN station_id END, CASE WHEN status IN (8, 400, 42) THEN ctime END) AS inbound_hub</t>
         </is>
       </c>
-      <c r="D25" s="39" t="n"/>
+      <c r="D25" s="10" t="n"/>
     </row>
     <row r="26" ht="28" customHeight="1">
       <c r="B26" s="56" t="inlineStr">
@@ -2392,7 +3540,7 @@
           <t>,min_by(next_station_id, ctime) filter (where status in (8,42,15,36,415,47,48) and next_station_id is not null and next_station_id != 0) next_station_id</t>
         </is>
       </c>
-      <c r="D26" s="39" t="n"/>
+      <c r="D26" s="10" t="n"/>
     </row>
     <row r="27" ht="28" customHeight="1">
       <c r="B27" s="56" t="inlineStr">
@@ -2405,7 +3553,7 @@
           <t>,min(if(status in (8, 400, 42), from_unixtime(ctime-3600), null)) soc_received</t>
         </is>
       </c>
-      <c r="D27" s="39" t="n"/>
+      <c r="D27" s="10" t="n"/>
     </row>
     <row r="28" ht="28" customHeight="1">
       <c r="B28" s="56" t="inlineStr">
@@ -2418,7 +3566,7 @@
           <t>,min(if(status in (33, 410, 44), from_unixtime(ctime-3600), null)) soc_packed</t>
         </is>
       </c>
-      <c r="D28" s="39" t="n"/>
+      <c r="D28" s="10" t="n"/>
     </row>
     <row r="29" ht="28" customHeight="1">
       <c r="B29" s="56" t="inlineStr">
@@ -2431,7 +3579,7 @@
           <t>,min(if(status in (35, 412, 46), from_unixtime(ctime-3600), null)) soc_lhpacked</t>
         </is>
       </c>
-      <c r="D29" s="39" t="n"/>
+      <c r="D29" s="10" t="n"/>
     </row>
     <row r="31" ht="22" customHeight="1">
       <c r="B31" s="27" t="inlineStr">
@@ -2439,8 +3587,8 @@
           <t>4. NORMALIZE TÊN STATION (Liên quan phân loại station)</t>
         </is>
       </c>
-      <c r="C31" s="28" t="n"/>
-      <c r="D31" s="29" t="n"/>
+      <c r="C31" s="9" t="n"/>
+      <c r="D31" s="10" t="n"/>
     </row>
     <row r="32" ht="56" customHeight="1">
       <c r="B32" s="12" t="inlineStr">
@@ -2453,8 +3601,8 @@
         ON ott.linehaul_task_id = td.trip_number</t>
         </is>
       </c>
-      <c r="C32" s="38" t="n"/>
-      <c r="D32" s="39" t="n"/>
+      <c r="C32" s="9" t="n"/>
+      <c r="D32" s="10" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="13">
@@ -2476,7 +3624,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Output/Ahamove/04. OPS_METRICS/2026-07-lh-offload-kpi-workflow-explained.xlsx
+++ b/Output/Ahamove/04. OPS_METRICS/2026-07-lh-offload-kpi-workflow-explained.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -123,6 +123,15 @@
       <b val="1"/>
       <i val="1"/>
       <color rgb="00FF7F32"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Arial"/>
       <sz val="9"/>
     </font>
   </fonts>
@@ -322,7 +331,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="72">
+  <cellXfs count="74">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -487,6 +496,8 @@
     <xf numFmtId="0" fontId="16" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -3630,7 +3641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -3928,6 +3939,24 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="B20" s="72" t="inlineStr">
+        <is>
+          <t>% Late Unload</t>
+        </is>
+      </c>
+      <c r="C20" s="73" t="inlineStr">
+        <is>
+          <t>Definition: Tỷ lệ đơn có mốc (sla_lhpacked_ontime - lh_transported) &lt; 2h.
+Calculation: Số đơn lỗi Late Unload / Total Late Orders</t>
+        </is>
+      </c>
+      <c r="D20" s="73" t="inlineStr">
+        <is>
+          <t>Đo lường tỷ trọng đơn bị trễ do Linehaul dỡ hàng quá sát giờ COT SOC (&lt; 2h buffer time)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B2:D2"/>
